--- a/config/tables/gas.ability_additional_cost.xlsx
+++ b/config/tables/gas.ability_additional_cost.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AbilityAdditionalCost" sheetId="1" r:id="R3e122056a1c84f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AbilityAdditionalCost" sheetId="1" r:id="R8bb9cd3f73e74957"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -297,8 +297,8 @@
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="23" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="35" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="35" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
   </x:cols>
@@ -311,15 +311,9 @@
         <x:v>id</x:v>
       </x:c>
       <x:c r="C1" s="4" t="str">
-        <x:v>ability_id</x:v>
+        <x:v>resource</x:v>
       </x:c>
       <x:c r="D1" s="4" t="str">
-        <x:v>order</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="str">
-        <x:v>resource</x:v>
-      </x:c>
-      <x:c r="F1" s="4" t="str">
         <x:v>amount</x:v>
       </x:c>
     </x:row>
@@ -331,15 +325,9 @@
         <x:v>int#range=[1,2147483647]</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>int#ref=gas.TbAbility</x:v>
+        <x:v>string#regex=^[A-Za-z0-9_]+(\.[A-Za-z0-9_]+)*$</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>int#range=[0,2147483647]</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="str">
-        <x:v>string#regex=^[A-Za-z0-9_]+(\.[A-Za-z0-9_]+)*$</x:v>
-      </x:c>
-      <x:c r="F2" s="6" t="str">
         <x:v>long#range=[1,4294967295]</x:v>
       </x:c>
     </x:row>
@@ -350,8 +338,6 @@
       <x:c r="B3" s="5"/>
       <x:c r="C3" s="5"/>
       <x:c r="D3" s="5"/>
-      <x:c r="E3" s="5"/>
-      <x:c r="F3" s="5"/>
     </x:row>
     <x:row r="4" ht="66" customHeight="1">
       <x:c r="A4" s="8" t="str">
@@ -361,15 +347,9 @@
         <x:v>Unique additional cost identifier.</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
-        <x:v>Owning ability identifier.</x:v>
+        <x:v>Stable dot-separated resource name resolved by the game provider.</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
-        <x:v>Cost order within the ability.</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="str">
-        <x:v>Stable dot-separated resource name resolved by the game provider.</x:v>
-      </x:c>
-      <x:c r="F4" s="8" t="str">
         <x:v>Positive quantity consumed on each commit.</x:v>
       </x:c>
     </x:row>
@@ -378,16 +358,10 @@
       <x:c r="B5" s="9" t="n">
         <x:v>10021</x:v>
       </x:c>
-      <x:c r="C5" s="9" t="n">
-        <x:v>1002</x:v>
+      <x:c r="C5" s="10" t="str">
+        <x:v>Inventory.Bomb</x:v>
       </x:c>
       <x:c r="D5" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="str">
-        <x:v>Inventory.Bomb</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
